--- a/raw_data/sapling_control_blocks_preharvest_sapling_regen_bld_data(19sept2025).xlsx
+++ b/raw_data/sapling_control_blocks_preharvest_sapling_regen_bld_data(19sept2025).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjs23\Documents\Projects\Slash Wall Research Data\Research Data\Station Road Slash Wall (started 9-9-2025 at 2pm)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjs23\Documents\R\slash-wall-vegetation\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B21637D-D650-48F7-9D0D-35F33D7D42F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A34A689-23D1-4C28-9F1B-4B3846F020BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D54CE094-C30C-4B8E-A49A-D49908DB7918}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11955" activeTab="1" xr2:uid="{D54CE094-C30C-4B8E-A49A-D49908DB7918}"/>
   </bookViews>
   <sheets>
     <sheet name="tally sheet" sheetId="1" r:id="rId1"/>
